--- a/healthcare_forms/027_restricted_antibiotic_request_form--healthcare_forms.xlsx
+++ b/healthcare_forms/027_restricted_antibiotic_request_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cefpodoxime</t>
+          <t>ceftazidime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cefpodoxime</t>
+          <t>Ceftazidime</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ceftazidime</t>
+          <t>ceftriaxone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ceftazidime</t>
+          <t>Ceftriaxone</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ceftriaxone</t>
+          <t>cefuoxime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ceftriaxone</t>
+          <t>Cefuoxime</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cefuoxime</t>
+          <t>cefpirome</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cefuoxime</t>
+          <t>Cefpirome</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cefpirome</t>
+          <t>ceftizoxime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cefpirome</t>
+          <t>Ceftizoxime</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ceftriaxone</t>
+          <t>ceftizidime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ceftriaxone</t>
+          <t>Ceftizidime</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ceftizoxime</t>
+          <t>cefpiroxime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ceftizoxime</t>
+          <t>Cefpiroxime</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cefepime</t>
+          <t>cefuroxime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cefepime</t>
+          <t>Cefuroxime</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ceftizidime</t>
+          <t>cefazimine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ceftizidime</t>
+          <t>Cefazimine</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cefpiroxime</t>
+          <t>cefazolin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cefpiroxime</t>
+          <t>Cefazolin</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cefuroxime</t>
+          <t>cefepimine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cefuroxime</t>
+          <t>Cefepimine</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cefazimine</t>
+          <t>ceftriaxine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cefazimine</t>
+          <t>Ceftriaxine</t>
         </is>
       </c>
     </row>
@@ -1222,214 +1222,129 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cefazolin</t>
+          <t>cefpiroime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cefazolin</t>
+          <t>Cefpiroime</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>antibiotic_info_choices</t>
+          <t>route_info_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cefaclor</t>
+          <t>inpatient</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cefaclor</t>
+          <t>Inpatient</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>antibiotic_info_choices</t>
+          <t>route_info_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cefepimine</t>
+          <t>outpatient</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cefepimine</t>
+          <t>Outpatient</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>antibiotic_info_choices</t>
+          <t>route_info_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ceftazidime</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ceftazidime</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>antibiotic_info_choices</t>
+          <t>route_info_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ceftriaxine</t>
+          <t>urgent_care</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ceftriaxine</t>
+          <t>Urgent Care</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>antibiotic_info_choices</t>
+          <t>approval_info_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cefpiroime</t>
+          <t>antimicrobial_stewardship_team</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cefpiroime</t>
+          <t>Antimicrobial Stewardship Team</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>route_info_choices</t>
+          <t>approval_info_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>inpatient</t>
+          <t>pharmacy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inpatient</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>route_info_choices</t>
+          <t>approval_info_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>outpatient</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Outpatient</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>route_info_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>emergency</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Emergency</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>route_info_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>urgent_care</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Urgent Care</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>approval_info_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>antimicrobial_stewardship_team</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Antimicrobial Stewardship Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>approval_info_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pharmacy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pharmacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>approval_info_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>clinical</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Clinical</t>
         </is>
